--- a/src-tauri/resources/input_template_new.xlsx
+++ b/src-tauri/resources/input_template_new.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班级" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课程" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课时标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,16 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -58,33 +54,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="009CA3AF"/>
-      </left>
-      <right style="thin">
-        <color rgb="009CA3AF"/>
-      </right>
-      <top style="thin">
-        <color rgb="009CA3AF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="009CA3AF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,6 +137,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>排课助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>只需填写参与排课决策的教师（语数英、物化生政史地等）。体育、艺术、体育活动等科目不需要填写教师，课表也不显示教师姓名。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,13 +443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,14 +460,14 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>教师姓名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>任教学科</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>教师姓名</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>职务</t>
@@ -482,134 +475,227 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>T01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张老师</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>语文</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>张老师</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>班主任</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>李老师</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>语文</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>李老师</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王老师</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>王老师</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>年级主任</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>班主任</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>T04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>赵老师</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>赵老师</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>刘老师</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>班主任</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>T05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>陈老师</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>刘老师</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>T06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>陈老师</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>周老师</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>说明：教师ID必填且唯一；职务填班主任/年级主任/教研组长等，无职务留空</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>吴老师</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>郑老师</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>孙老师</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>政治</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>钱老师</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>冯老师</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>地理</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -619,27 +705,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>班级ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>班级名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>班级ID</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>年级</t>
@@ -657,117 +743,83 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>高二(1)班</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>高二</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>张老师</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>物化生</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>高二(2)班</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>物化地</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>高二(3)班</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>政史地</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>高二(2)班</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>李老师</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>政史地</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>高二(3)班</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>王老师</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>物化生</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>高二(4)班</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>赵老师</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>物化地</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>说明：班级ID必填且唯一；选科填三门组合如物化生/物化地/政史地/史政地等</t>
         </is>
       </c>
     </row>
@@ -782,313 +834,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>班级ID</t>
+          <t>学科</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>学科</t>
+          <t>选考周课时</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>教师ID</t>
+          <t>非选考周课时</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>周课时</t>
+          <t>连堂节数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>连堂节数</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>单双周</t>
+          <t>连堂日</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>语文</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>T01</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="B2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
+      <c r="E2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="B3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>T05</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="B4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>政治</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>历史</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="n">
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>地理</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>地理</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="n">
+      <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>体育活动</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>艺术</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>班会</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="n">
+      <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>研究性学习</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>校本课</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="n">
+      <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>每周</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>说明：(班级ID,学科)必须唯一；周课时必填正整数；连堂节数仅语数英可填2，其他填0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>固定课（班会/研究性学习/校本课）必须填行，教师ID留空；自习不需填行，内核自动补齐</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
